--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Bakery_20251102.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Bakery_20251102.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,276 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DUO71010</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bag - Paper (10#)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22.51</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>45.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SMTSM2PIKN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Napkin - Dispenser</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30.94</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TS8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 8oz</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>38.29</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>153.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>460200</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hand Soap - Foaming</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>43.18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>86.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bag - Wax (Sandwich)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>113.57</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>227.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FLOW15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>71.60</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>71.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INPSDR0120ITHACABAKERY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cup - Hot (12oz)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>62.78</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>125.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INPSDR0160ITHACABAKERY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cup - Hot (16oz)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>70.09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>140.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INPSDR0200ITHACABAKERY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cup - Hot (20oz)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>83.13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>83.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JNA26W</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Straws - Wrapped</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>59.31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>59.31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
